--- a/artfynd/A 45-2022 artfynd.xlsx
+++ b/artfynd/A 45-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45-2022 artfynd.xlsx
+++ b/artfynd/A 45-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>64188797</v>
       </c>
       <c r="B2" t="n">
-        <v>104188</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443671.6464480888</v>
+        <v>443672</v>
       </c>
       <c r="R2" t="n">
-        <v>6171113.939577396</v>
+        <v>6171114</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2004-08-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-08-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,12 +794,7 @@
         <v>64188801</v>
       </c>
       <c r="B3" t="n">
-        <v>99780</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102072</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443671.6464480888</v>
+        <v>443672</v>
       </c>
       <c r="R3" t="n">
-        <v>6171113.939577396</v>
+        <v>6171114</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,21 +859,11 @@
           <t>2004-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2004-08-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>Aphanes inexspectata/2D4i3930/Vitaby s:n/BSl/ /Bengt Sandkull,Lund</t>
@@ -915,7 +885,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Lund-Botaniska/Zoologiska museet</t>
+          <t>Biologiska Museet, Lunds Universitet</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">

--- a/artfynd/A 45-2022 artfynd.xlsx
+++ b/artfynd/A 45-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64188797</v>
       </c>
       <c r="B2" t="n">
-        <v>106669</v>
+        <v>106681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>64188801</v>
       </c>
       <c r="B3" t="n">
-        <v>102072</v>
+        <v>102077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45-2022 artfynd.xlsx
+++ b/artfynd/A 45-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64188797</v>
       </c>
       <c r="B2" t="n">
-        <v>106681</v>
+        <v>106690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>64188801</v>
       </c>
       <c r="B3" t="n">
-        <v>102077</v>
+        <v>102083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45-2022 artfynd.xlsx
+++ b/artfynd/A 45-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64188797</v>
       </c>
       <c r="B2" t="n">
-        <v>106690</v>
+        <v>106695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>64188801</v>
       </c>
       <c r="B3" t="n">
-        <v>102083</v>
+        <v>102084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45-2022 artfynd.xlsx
+++ b/artfynd/A 45-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64188797</v>
       </c>
       <c r="B2" t="n">
-        <v>106695</v>
+        <v>106723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>64188801</v>
       </c>
       <c r="B3" t="n">
-        <v>102084</v>
+        <v>102111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45-2022 artfynd.xlsx
+++ b/artfynd/A 45-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64188797</v>
       </c>
       <c r="B2" t="n">
-        <v>106723</v>
+        <v>106729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>64188801</v>
       </c>
       <c r="B3" t="n">
-        <v>102111</v>
+        <v>102117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45-2022 artfynd.xlsx
+++ b/artfynd/A 45-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64188797</v>
       </c>
       <c r="B2" t="n">
-        <v>106729</v>
+        <v>106736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>64188801</v>
       </c>
       <c r="B3" t="n">
-        <v>102117</v>
+        <v>102124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45-2022 artfynd.xlsx
+++ b/artfynd/A 45-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64188797</v>
       </c>
       <c r="B2" t="n">
-        <v>106736</v>
+        <v>106740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>64188801</v>
       </c>
       <c r="B3" t="n">
-        <v>102124</v>
+        <v>102128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45-2022 artfynd.xlsx
+++ b/artfynd/A 45-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64188797</v>
       </c>
       <c r="B2" t="n">
-        <v>106740</v>
+        <v>106747</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>64188801</v>
       </c>
       <c r="B3" t="n">
-        <v>102128</v>
+        <v>102135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45-2022 artfynd.xlsx
+++ b/artfynd/A 45-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64188797</v>
       </c>
       <c r="B2" t="n">
-        <v>106750</v>
+        <v>106755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>64188801</v>
       </c>
       <c r="B3" t="n">
-        <v>102138</v>
+        <v>102143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45-2022 artfynd.xlsx
+++ b/artfynd/A 45-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64188797</v>
       </c>
       <c r="B2" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>64188801</v>
       </c>
       <c r="B3" t="n">
-        <v>102143</v>
+        <v>102151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45-2022 artfynd.xlsx
+++ b/artfynd/A 45-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>64188797</v>
       </c>
       <c r="B2" t="n">
-        <v>106763</v>
+        <v>106773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>64188801</v>
       </c>
       <c r="B3" t="n">
-        <v>102151</v>
+        <v>102161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45-2022 artfynd.xlsx
+++ b/artfynd/A 45-2022 artfynd.xlsx
@@ -675,48 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64188797</v>
+        <v>98421172</v>
       </c>
       <c r="B2" t="n">
-        <v>106773</v>
+        <v>79844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221647</v>
+        <v>144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mjukdån</t>
+          <t>Stor knopplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galeopsis ladanum</t>
+          <t>Mycobilimbia pilularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Körb.) Hafellner &amp; Türk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>350m O Axlahult, Sk</t>
+          <t>Simrishamn, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443672</v>
+        <v>443552</v>
       </c>
       <c r="R2" t="n">
-        <v>6171114</v>
+        <v>6171101</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +741,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2004-08-19</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2004-08-19</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Galeopsis ladanum/2D4i3930/Vitaby s:n/BSl/ /Bengt Sandkull,Lund</t>
+          <t>Gammal bok</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,40 +762,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>skogsväg och husruin</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>SkFlora    859801</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Elisabeth Arvidsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Sandkull</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Elisabeth Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>64188801</v>
+        <v>98421112</v>
       </c>
       <c r="B3" t="n">
-        <v>102161</v>
+        <v>77726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,37 +789,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1707</v>
+        <v>1342</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Småjungfrukam</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aphanes australis</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Rydb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>350m O Axlahult, Sk</t>
+          <t>Simrishamn, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443672</v>
+        <v>443573</v>
       </c>
       <c r="R3" t="n">
-        <v>6171114</v>
+        <v>6171086</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,17 +848,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2004-08-19</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2004-08-19</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Aphanes inexspectata/2D4i3930/Vitaby s:n/BSl/ /Bengt Sandkull,Lund</t>
+          <t>Gammal bok</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,50 +869,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>skogsväg och husruin</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Biologiska Museet, Lunds Universitet</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>SkFlora    859805</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Elisabeth Arvidsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Sandkull</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Elisabeth Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98420037</v>
+        <v>64188801</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,42 +896,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1707</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Småjungfrukam</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Aphanes australis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>Rydb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Simrishamn, Sk</t>
+          <t>350m O Axlahult, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443555.0386518209</v>
+        <v>443672</v>
       </c>
       <c r="R4" t="n">
-        <v>6171095.717386509</v>
+        <v>6171114</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +950,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Aphanes inexspectata/2D4i3930/Vitaby s:n/BSl/ /Bengt Sandkull,Lund</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,56 +971,74 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>skogsväg och husruin</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>SkFlora    859805</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elisabeth Arvidsson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elisabeth Arvidsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Bengt Sandkull</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98421172</v>
+        <v>98420037</v>
       </c>
       <c r="B5" t="n">
-        <v>78005</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>144</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor knopplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mycobilimbia pilularis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Körb.) Hafellner &amp; Türk</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443552.2874928888</v>
+        <v>443556</v>
       </c>
       <c r="R5" t="n">
-        <v>6171101.390063473</v>
+        <v>6171096</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1103,24 +1079,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gammal bok</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,15 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98421112</v>
+        <v>64188797</v>
       </c>
       <c r="B6" t="n">
-        <v>75910</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,42 +1119,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1342</v>
+        <v>221647</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Mjukdån</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Galeopsis ladanum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Simrishamn, Sk</t>
+          <t>350m O Axlahult, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443572.9962414253</v>
+        <v>443672</v>
       </c>
       <c r="R6" t="n">
-        <v>6171086.465696094</v>
+        <v>6171114</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,27 +1173,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-19</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gammal bok</t>
+          <t>Galeopsis ladanum/2D4i3930/Vitaby s:n/BSl/ /Bengt Sandkull,Lund</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,19 +1194,33 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>skogsväg och husruin</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>SkFlora    859801</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elisabeth Arvidsson</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elisabeth Arvidsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Bengt Sandkull</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
